--- a/data/trans_dic/IP18_E_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP18_E_R-Estudios-trans_dic.xlsx
@@ -717,37 +717,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>94,89; 100,0</t>
+          <t>94,32; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>96,13; 100,0</t>
+          <t>96,11; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92,23; 100,0</t>
+          <t>91,43; 100,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55,1; 100,0</t>
+          <t>67,73; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,21; 100,0</t>
+          <t>95,26; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,34; 100,0</t>
+          <t>96,07; 100,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,51; 100,0</t>
+          <t>92,92; 100,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>96,65; 99,69</t>
+          <t>96,58; 99,68</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>97,13; 100,0</t>
+          <t>97,56; 100,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>94,6; 99,47</t>
+          <t>94,6; 99,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>83,47; 100,0</t>
+          <t>87,53; 100,0</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>93,3; 96,9</t>
+          <t>93,37; 96,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>93,96; 97,19</t>
+          <t>93,91; 97,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94,12; 97,17</t>
+          <t>94,29; 97,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69,36; 92,32</t>
+          <t>70,86; 92,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>93,22; 96,89</t>
+          <t>93,18; 96,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>94,27; 97,33</t>
+          <t>94,27; 97,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,91; 97,85</t>
+          <t>95,05; 97,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>93,24; 98,92</t>
+          <t>93,09; 98,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>94,13; 96,45</t>
+          <t>94,0; 96,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>94,86; 97,06</t>
+          <t>94,77; 96,95</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>95,15; 97,21</t>
+          <t>95,09; 97,17</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>84,7; 95,26</t>
+          <t>86,18; 95,41</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>81,7; 90,53</t>
+          <t>82,25; 90,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84,44; 92,95</t>
+          <t>84,06; 92,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82,69; 91,44</t>
+          <t>82,13; 91,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>65,27; 88,21</t>
+          <t>64,46; 87,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>77,88; 87,97</t>
+          <t>77,09; 87,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>84,15; 92,5</t>
+          <t>83,66; 91,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81,18; 90,07</t>
+          <t>80,96; 90,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>68,24; 93,06</t>
+          <t>67,35; 92,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>81,76; 88,04</t>
+          <t>81,72; 88,42</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>85,76; 91,46</t>
+          <t>85,95; 91,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>83,57; 89,6</t>
+          <t>83,44; 89,52</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>70,98; 88,6</t>
+          <t>69,82; 88,23</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>91,89; 95,08</t>
+          <t>91,94; 94,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>93,15; 96,03</t>
+          <t>93,02; 96,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92,44; 95,38</t>
+          <t>92,38; 95,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74,35; 89,42</t>
+          <t>73,68; 89,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,37 +1162,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,14; 95,92</t>
+          <t>93,21; 96,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,6; 95,5</t>
+          <t>92,6; 95,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>89,6; 96,71</t>
+          <t>89,59; 96,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>92,11; 94,33</t>
+          <t>92,1; 94,41</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93,65; 95,65</t>
+          <t>93,68; 95,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>92,98; 95,07</t>
+          <t>92,93; 95,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,51; 92,72</t>
+          <t>84,54; 92,72</t>
         </is>
       </c>
     </row>
@@ -1504,37 +1504,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>67097; 70711</t>
+          <t>66694; 70711</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>83738; 87113</t>
+          <t>83720; 87113</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51016; 55312</t>
+          <t>50569; 55312</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3607; 6545</t>
+          <t>4433; 6545</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>68584; 72031</t>
+          <t>68617; 72031</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>75430; 78293</t>
+          <t>75214; 78293</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58440; 62497</t>
+          <t>58075; 62497</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1544,22 +1544,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>137957; 142293</t>
+          <t>137865; 142289</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>160663; 165406</t>
+          <t>161362; 165406</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>111449; 117180</t>
+          <t>111450; 117168</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13338; 15979</t>
+          <t>13987; 15979</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>341149; 354318</t>
+          <t>341418; 354555</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>398255; 411937</t>
+          <t>398009; 412384</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>411177; 424517</t>
+          <t>411911; 425098</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45946; 61151</t>
+          <t>46938; 61201</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>376036; 390831</t>
+          <t>375891; 390378</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>441018; 455325</t>
+          <t>441025; 455621</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>414206; 427011</t>
+          <t>414810; 427111</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>85082; 90261</t>
+          <t>84943; 90275</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>723881; 741707</t>
+          <t>722880; 741670</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>845806; 865471</t>
+          <t>845040; 864500</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>830936; 848922</t>
+          <t>830428; 848586</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>133398; 150024</t>
+          <t>135719; 150255</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>124695; 138169</t>
+          <t>125531; 138844</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>130942; 144127</t>
+          <t>130354; 143401</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>127863; 141384</t>
+          <t>126999; 140825</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17969; 24284</t>
+          <t>17746; 24118</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>106832; 120676</t>
+          <t>105750; 120251</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>138873; 152654</t>
+          <t>138074; 151693</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>138134; 153258</t>
+          <t>137748; 153369</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21092; 28764</t>
+          <t>20817; 28556</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>236931; 255133</t>
+          <t>236821; 256242</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>274521; 292750</t>
+          <t>275132; 292708</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>271414; 291000</t>
+          <t>270989; 290745</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>41484; 51778</t>
+          <t>40805; 51561</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>541227; 559988</t>
+          <t>541509; 559492</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>620381; 639591</t>
+          <t>619523; 640023</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>597946; 616934</t>
+          <t>597539; 616918</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>74582; 89702</t>
+          <t>73912; 89845</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>559159; 579433</t>
+          <t>559176; 579435</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>662403; 682176</t>
+          <t>662898; 682766</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>619551; 638985</t>
+          <t>619529; 638715</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>117908; 127257</t>
+          <t>117893; 127020</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1106733; 1133410</t>
+          <t>1106676; 1134445</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1289666; 1317211</t>
+          <t>1290116; 1317305</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1223471; 1251004</t>
+          <t>1222887; 1251511</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>195974; 215015</t>
+          <t>196061; 215028</t>
         </is>
       </c>
     </row>
